--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CAPACETE 13_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CAPACETE 13_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +482,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -495,7 +503,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -512,7 +524,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -529,7 +545,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -546,7 +566,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -560,10 +584,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -580,7 +608,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -597,7 +629,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -618,7 +654,211 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7898483640096</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CAPACETE VERMELHO SAN MARINO 58</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7898483667635</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CAPACETE SAN MARINO BRANCO 62</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7898483640102</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CAPACETE SAN MARINO VERMELHO 60</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7898483640164</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CAPACETE SAN MARINO PRETO FOSCO 60</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7898483640461</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CAPACETE SAN MARINO BRANCO 60</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 7898483667581</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CAPACETE SAN MARINO VERMELHO 62</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7898483667574</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CAPACETE  SAN MARINO PRETO 62</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7898483640034</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAPACETE SAN MARINO PRETO 58 </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CAPACETE 13_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CAPACETE 13_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,11 +488,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,11 +504,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,11 +520,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,11 +536,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -587,11 +552,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -608,11 +568,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -629,11 +584,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -654,11 +604,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -679,11 +624,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -704,11 +644,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -729,11 +664,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -754,11 +684,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -779,11 +704,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -804,11 +724,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -829,11 +744,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -852,11 +762,6 @@
       <c r="D19" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>220</t>
         </is>
       </c>
     </row>
